--- a/docs/xiuxian/tracking_dictionary_template_xiuxian_supplemented.xlsx
+++ b/docs/xiuxian/tracking_dictionary_template_xiuxian_supplemented.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="_说明" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6159" uniqueCount="1817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6164" uniqueCount="1824">
   <si>
     <t>项目</t>
   </si>
@@ -5486,13 +5486,131 @@
   </si>
   <si>
     <t>来源字段 userinfo 中的 JSON 属性 regtype</t>
+  </si>
+  <si>
+    <t>date</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>timestamp</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件精确发生时间，底层为13位 Unix 毫秒时间戳（BIGINT），例如 1783525080422。不是秒级时间戳；转换时使用 FROM_UNIXTIME(time / 1000)。业务日期或按自然日统计优先使用 dt。</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前数据源是阿里云</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> AnalyticDB MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>兼容引擎，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">CTE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以阿里云</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> AnalyticDB MySQL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>语法为主</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生成</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生成</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务日期（分区字段），底层为8位 YYYYMMDD 整数（BIGINT），例如 20260715 表示 2026-07-15。不是 Unix 时间戳，不得使用 FROM_UNIXTIME 或 UNIX_TIMESTAMP。选择 dt 作为时间字段时，日期展示、筛选、分组和排序都必须基于 dt。日期分区字段 dt 的边界必须先通过
+DATE_FORMAT(&lt;日期表达式&gt;, '%Y%m%d') 格式化，再 CAST AS BIGINT</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5532,6 +5650,19 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -5758,7 +5889,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -5861,6 +5992,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -24632,7 +24769,8 @@
     <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="28" style="1" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="93.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -24663,12 +24801,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="27">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>54</v>
+      <c r="C3" s="36" t="s">
+        <v>1818</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>1819</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -24775,7 +24916,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
@@ -24783,7 +24924,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>1353</v>
       </c>
@@ -24791,15 +24932,18 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:5" ht="54">
       <c r="A19" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="C19" s="35" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>1355</v>
       </c>
@@ -24807,7 +24951,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>35</v>
       </c>
@@ -24818,6 +24962,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -24978,10 +25123,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="71.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="68.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24998,9 +25146,24 @@
         <v>1359</v>
       </c>
     </row>
+    <row r="2" spans="1:4" ht="30">
+      <c r="A2" s="36" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
